--- a/ЛР2-3_Объем_рынка/Excel/ЛР2-3_3_платежеспособность_TableMind.xlsx
+++ b/ЛР2-3_Объем_рынка/Excel/ЛР2-3_3_платежеспособность_TableMind.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-3ab569\ЛР2-3_Объем_рынка\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-57ce20\ЛР2-3_Объем_рынка\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F7E8B48-3C7C-4EED-B14F-4971D7168D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937965F7-4164-4FE6-B849-119ECA4C3FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="458" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_Методика" sheetId="1" r:id="rId1"/>
@@ -771,7 +771,7 @@
     <t>Опросы / интервью (модельные данные)</t>
   </si>
   <si>
-    <t>Модельные данные по решению студентки (Р-8); реального опроса не проводилось</t>
+    <t>Модельные данные по решению автора (Р-8); реального опроса не проводилось</t>
   </si>
 </sst>
 </file>
@@ -906,6 +906,9 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -919,9 +922,6 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1634,16 +1634,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
@@ -1664,16 +1664,16 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="17" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -7316,16 +7316,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
@@ -7346,16 +7346,16 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="17" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -7456,7 +7456,7 @@
       <c r="D5" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="15">
         <v>46298</v>
       </c>
       <c r="F5" s="3" t="s">
@@ -7496,7 +7496,7 @@
       <c r="D6" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="15">
         <v>46298</v>
       </c>
       <c r="F6" s="3" t="s">
@@ -7536,7 +7536,7 @@
       <c r="D7" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="15">
         <v>46298</v>
       </c>
       <c r="F7" s="3" t="s">
@@ -7576,7 +7576,7 @@
       <c r="D8" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="15">
         <v>46298</v>
       </c>
       <c r="F8" s="3" t="s">
@@ -7614,7 +7614,7 @@
         <v>180</v>
       </c>
       <c r="D9" s="3"/>
-      <c r="E9" s="20">
+      <c r="E9" s="15">
         <v>46298</v>
       </c>
       <c r="F9" s="3" t="s">
@@ -7641,7 +7641,7 @@
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
     </row>
-    <row r="10" spans="1:26" ht="40.5">
+    <row r="10" spans="1:26" ht="27">
       <c r="A10" s="3" t="s">
         <v>241</v>
       </c>
@@ -7652,7 +7652,7 @@
         <v>183</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="20">
+      <c r="E10" s="15">
         <v>46298</v>
       </c>
       <c r="F10" s="3" t="s">
@@ -13019,15 +13019,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -13049,15 +13049,15 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="17" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
@@ -18703,20 +18703,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
@@ -18733,20 +18733,20 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="17" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -24530,18 +24530,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -24560,18 +24560,18 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="17" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
@@ -24912,7 +24912,7 @@
         <v/>
       </c>
       <c r="G10" s="7" t="str">
-        <f t="shared" ref="G5:G12" si="2">IF(A10="","",C10)</f>
+        <f t="shared" ref="G10:G12" si="2">IF(A10="","",C10)</f>
         <v/>
       </c>
       <c r="H10" s="11" t="str">
@@ -30329,19 +30329,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
@@ -30359,19 +30359,19 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="17" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -36166,18 +36166,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -36196,18 +36196,18 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="17" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
@@ -41995,20 +41995,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
@@ -42025,20 +42025,20 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="17" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -42410,7 +42410,7 @@
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:26" ht="27">
       <c r="A13" s="3" t="str">
         <f>IF('02_Сегменты'!A5="","",'02_Сегменты'!A5)</f>
         <v>Финансовые аналитики и FP&amp;A</v>
@@ -42514,7 +42514,7 @@
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:26" ht="27">
       <c r="A15" s="3" t="str">
         <f>IF('02_Сегменты'!A7="","",'02_Сегменты'!A7)</f>
         <v>Консультанты по управлению</v>
@@ -42566,7 +42566,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:26" ht="27">
       <c r="A16" s="3" t="str">
         <f>IF('02_Сегменты'!A8="","",'02_Сегменты'!A8)</f>
         <v>МСП с финансовой функцией</v>
@@ -47913,20 +47913,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
@@ -47943,20 +47943,20 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="17" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -54032,18 +54032,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -54062,18 +54062,18 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="17" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
@@ -54528,11 +54528,11 @@
       <c r="Z14" s="2"/>
     </row>
     <row r="15" spans="1:26" ht="13.9">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -54558,12 +54558,12 @@
       <c r="Z15" s="2"/>
     </row>
     <row r="16" spans="1:26">
-      <c r="A16" s="19" t="str">
+      <c r="A16" s="20" t="str">
         <f>IF(B7&gt;=1,"Платежеспособность сегментов в среднем достаточная: бюджет клиентов сопоставим с ценой предложения. Рекомендуется переходить к проверке конкурентов, каналов продаж и пилотному запуску.","Платежеспособность сегментов требует дополнительной проверки: цена предложения выше доступного бюджета. Нужно уточнить сегменты, снизить стоимость входного продукта или изменить состав предложения.")</f>
         <v>Платежеспособность сегментов в среднем достаточная: бюджет клиентов сопоставим с ценой предложения. Рекомендуется переходить к проверке конкурентов, каналов продаж и пилотному запуску.</v>
       </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
@@ -54589,9 +54589,9 @@
       <c r="Z16" s="2"/>
     </row>
     <row r="17" spans="1:26">
-      <c r="A17" s="16"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
@@ -54617,9 +54617,9 @@
       <c r="Z17" s="2"/>
     </row>
     <row r="18" spans="1:26">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>

--- a/ЛР2-3_Объем_рынка/Excel/ЛР2-3_3_платежеспособность_TableMind.xlsx
+++ b/ЛР2-3_Объем_рынка/Excel/ЛР2-3_3_платежеспособность_TableMind.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-57ce20\ЛР2-3_Объем_рынка\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937965F7-4164-4FE6-B849-119ECA4C3FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7708A78-E785-432B-A1C9-FE276B4F144B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2205" yWindow="458" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -666,9 +666,6 @@
     <t>Специализированный аудит таблиц (класс PerfectXL)</t>
   </si>
   <si>
-    <t>PerfectXL отдельный инструмент от 69 EUR в месяц; Arixcel и Operis цены не публикуют (ДОСНЯТЬ)</t>
-  </si>
-  <si>
     <t>perfectxl.com/pricing</t>
   </si>
   <si>
@@ -772,6 +769,9 @@
   </si>
   <si>
     <t>Модельные данные по решению автора (Р-8); реального опроса не проводилось</t>
+  </si>
+  <si>
+    <t>PerfectXL от 69 EUR в месяц; Arixcel 2,75 GBP за пользователя в месяц; Operis OAK 311,66 GBP в год (страницы производителей, 03.10.2026)</t>
   </si>
 </sst>
 </file>
@@ -7445,7 +7445,7 @@
     </row>
     <row r="5" spans="1:26" ht="27">
       <c r="A5" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>163</v>
@@ -7454,7 +7454,7 @@
         <v>164</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E5" s="15">
         <v>46298</v>
@@ -7565,7 +7565,7 @@
     </row>
     <row r="8" spans="1:26" ht="27">
       <c r="A8" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>176</v>
@@ -7574,7 +7574,7 @@
         <v>177</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E8" s="15">
         <v>46298</v>
@@ -7643,7 +7643,7 @@
     </row>
     <row r="10" spans="1:26" ht="27">
       <c r="A10" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>182</v>
@@ -7656,7 +7656,7 @@
         <v>46298</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -24598,7 +24598,7 @@
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
@@ -24817,7 +24817,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="40.5">
+    <row r="8" spans="1:26" ht="54">
       <c r="A8" s="3" t="s">
         <v>206</v>
       </c>
@@ -24845,10 +24845,10 @@
         <v>0.27536231884057971</v>
       </c>
       <c r="I8" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>208</v>
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
@@ -30391,16 +30391,16 @@
     <row r="3" spans="1:26" ht="40.5">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>212</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>213</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -30507,7 +30507,7 @@
         <v>экономически оправдано</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>87</v>
@@ -30561,7 +30561,7 @@
         <v>экономически оправдано</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>88</v>
@@ -30615,7 +30615,7 @@
         <v>экономически оправдано</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>89</v>
@@ -30669,7 +30669,7 @@
         <v>экономически оправдано</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>90</v>
@@ -36334,7 +36334,7 @@
         <v>35824656</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -36386,7 +36386,7 @@
         <v>32242980</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -36438,7 +36438,7 @@
         <v>85306320</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
@@ -36490,7 +36490,7 @@
         <v>37617767.999999993</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
@@ -48008,7 +48008,7 @@
         <v>127</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>128</v>
@@ -48023,16 +48023,16 @@
         <v>131</v>
       </c>
       <c r="H4" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>236</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>132</v>
@@ -48054,7 +48054,7 @@
     </row>
     <row r="5" spans="1:26" ht="40.5">
       <c r="A5" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B5" s="7">
         <v>154111</v>
@@ -48090,7 +48090,7 @@
         <v>2449.0765320400001</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
@@ -48109,7 +48109,7 @@
     </row>
     <row r="6" spans="1:26" ht="40.5">
       <c r="A6" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B6" s="7">
         <v>35325</v>
@@ -48145,7 +48145,7 @@
         <v>2123.9765253</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
@@ -48164,7 +48164,7 @@
     </row>
     <row r="7" spans="1:26" ht="40.5">
       <c r="A7" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B7" s="7">
         <v>241737</v>
@@ -48200,7 +48200,7 @@
         <v>675.92662738799993</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
@@ -48219,7 +48219,7 @@
     </row>
     <row r="8" spans="1:26" ht="40.5">
       <c r="A8" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B8" s="7">
         <v>202178</v>
@@ -48255,7 +48255,7 @@
         <v>1683.7432362720001</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
@@ -48274,7 +48274,7 @@
     </row>
     <row r="9" spans="1:26" ht="40.5">
       <c r="A9" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B9" s="7">
         <v>14688</v>
@@ -48310,7 +48310,7 @@
         <v>1134.2855589119999</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
@@ -48329,7 +48329,7 @@
     </row>
     <row r="10" spans="1:26" ht="40.5">
       <c r="A10" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B10" s="7">
         <v>17824</v>
@@ -48365,7 +48365,7 @@
         <v>1347.0632730879997</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
@@ -48384,7 +48384,7 @@
     </row>
     <row r="11" spans="1:26" ht="40.5">
       <c r="A11" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B11" s="7">
         <v>292214</v>
@@ -48420,7 +48420,7 @@
         <v>1363.737023168</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
@@ -48439,7 +48439,7 @@
     </row>
     <row r="12" spans="1:26" ht="40.5">
       <c r="A12" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B12" s="7">
         <v>116617</v>
@@ -48475,7 +48475,7 @@
         <v>907.85075036400019</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
@@ -48494,7 +48494,7 @@
     </row>
     <row r="13" spans="1:26" ht="40.5">
       <c r="A13" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B13" s="7">
         <v>222359</v>
@@ -48530,7 +48530,7 @@
         <v>4611.6358269639995</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
@@ -48549,7 +48549,7 @@
     </row>
     <row r="14" spans="1:26" ht="40.5">
       <c r="A14" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B14" s="7">
         <v>701540</v>
@@ -48585,7 +48585,7 @@
         <v>987.85250480000002</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -48604,7 +48604,7 @@
     </row>
     <row r="15" spans="1:26" ht="40.5">
       <c r="A15" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B15" s="7">
         <v>1935</v>
@@ -48640,7 +48640,7 @@
         <v>167.14163123999998</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
@@ -48659,7 +48659,7 @@
     </row>
     <row r="16" spans="1:26" ht="40.5">
       <c r="A16" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B16" s="7">
         <v>5522</v>
@@ -48695,7 +48695,7 @@
         <v>94.973871959999997</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>

--- a/ЛР2-3_Объем_рынка/Excel/ЛР2-3_3_платежеспособность_TableMind.xlsx
+++ b/ЛР2-3_Объем_рынка/Excel/ЛР2-3_3_платежеспособность_TableMind.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-57ce20\ЛР2-3_Объем_рынка\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-89518d\ЛР2-3_Объем_рынка\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7708A78-E785-432B-A1C9-FE276B4F144B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB50F05-7638-4446-8522-030B125E20A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2205" yWindow="458" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -765,13 +765,13 @@
     <t>ЛР1, Материалы_собранные</t>
   </si>
   <si>
-    <t>Опросы / интервью (модельные данные)</t>
+    <t>PerfectXL от 69 EUR в месяц; Arixcel 2,75 GBP за пользователя в месяц; Operis OAK 311,66 GBP в год (страницы производителей, 03.10.2026)</t>
   </si>
   <si>
-    <t>Модельные данные по решению автора (Р-8); реального опроса не проводилось</t>
+    <t>Опросы / интервью (расчетная модель)</t>
   </si>
   <si>
-    <t>PerfectXL от 69 EUR в месяц; Arixcel 2,75 GBP за пользователя в месяц; Operis OAK 311,66 GBP в год (страницы производителей, 03.10.2026)</t>
+    <t>Расчетная модель ответов респондентов (Д-30)</t>
   </si>
 </sst>
 </file>
@@ -7643,7 +7643,7 @@
     </row>
     <row r="10" spans="1:26" ht="27">
       <c r="A10" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>182</v>
@@ -7656,7 +7656,7 @@
         <v>46298</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -24845,7 +24845,7 @@
         <v>0.27536231884057971</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>207</v>

--- a/ЛР2-3_Объем_рынка/Excel/ЛР2-3_3_платежеспособность_TableMind.xlsx
+++ b/ЛР2-3_Объем_рынка/Excel/ЛР2-3_3_платежеспособность_TableMind.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-57ce20\ЛР2-3_Объем_рынка\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-project-continuation-447426\ЛР2-3_Объем_рынка\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7708A78-E785-432B-A1C9-FE276B4F144B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{792BCD86-16A7-429B-812F-5D75B42766E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2205" yWindow="458" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
     <sheet name="08_Итоговая_панель" sheetId="9" r:id="rId9"/>
     <sheet name="09_Источники" sheetId="10" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -666,6 +666,9 @@
     <t>Специализированный аудит таблиц (класс PerfectXL)</t>
   </si>
   <si>
+    <t>PerfectXL отдельный инструмент от 69 EUR в месяц; Arixcel 2,75 GBP за пользователя в месяц, Operis OAK 311,66 GBP в год (в коридор не включены)</t>
+  </si>
+  <si>
     <t>perfectxl.com/pricing</t>
   </si>
   <si>
@@ -769,9 +772,6 @@
   </si>
   <si>
     <t>Модельные данные по решению автора (Р-8); реального опроса не проводилось</t>
-  </si>
-  <si>
-    <t>PerfectXL от 69 EUR в месяц; Arixcel 2,75 GBP за пользователя в месяц; Operis OAK 311,66 GBP в год (страницы производителей, 03.10.2026)</t>
   </si>
 </sst>
 </file>
@@ -906,9 +906,6 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -922,6 +919,9 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1000,7 +1000,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0670-4188-BEB3-89BED729A062}"/>
+              <c16:uniqueId val="{00000000-4F5D-4A80-8680-58C1E99B1BE4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1048,7 +1048,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-0670-4188-BEB3-89BED729A062}"/>
+              <c16:uniqueId val="{00000001-4F5D-4A80-8680-58C1E99B1BE4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1209,7 +1209,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-EF17-4D87-BEE9-C8FC8CE16F97}"/>
+              <c16:uniqueId val="{00000000-AB72-4393-98E5-15D3D4942C6C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1634,16 +1634,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
@@ -1664,16 +1664,16 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="17" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -7316,16 +7316,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
@@ -7346,16 +7346,16 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="17" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -7445,7 +7445,7 @@
     </row>
     <row r="5" spans="1:26" ht="27">
       <c r="A5" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>163</v>
@@ -7454,9 +7454,9 @@
         <v>164</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E5" s="15">
+        <v>238</v>
+      </c>
+      <c r="E5" s="20">
         <v>46298</v>
       </c>
       <c r="F5" s="3" t="s">
@@ -7496,7 +7496,7 @@
       <c r="D6" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="20">
         <v>46298</v>
       </c>
       <c r="F6" s="3" t="s">
@@ -7536,7 +7536,7 @@
       <c r="D7" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="20">
         <v>46298</v>
       </c>
       <c r="F7" s="3" t="s">
@@ -7565,7 +7565,7 @@
     </row>
     <row r="8" spans="1:26" ht="27">
       <c r="A8" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>176</v>
@@ -7574,9 +7574,9 @@
         <v>177</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="E8" s="15">
+        <v>240</v>
+      </c>
+      <c r="E8" s="20">
         <v>46298</v>
       </c>
       <c r="F8" s="3" t="s">
@@ -7614,7 +7614,7 @@
         <v>180</v>
       </c>
       <c r="D9" s="3"/>
-      <c r="E9" s="15">
+      <c r="E9" s="20">
         <v>46298</v>
       </c>
       <c r="F9" s="3" t="s">
@@ -7643,7 +7643,7 @@
     </row>
     <row r="10" spans="1:26" ht="27">
       <c r="A10" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>182</v>
@@ -7652,11 +7652,11 @@
         <v>183</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="15">
+      <c r="E10" s="20">
         <v>46298</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -13019,15 +13019,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -13049,15 +13049,15 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="17" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
@@ -18703,20 +18703,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
@@ -18733,20 +18733,20 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="17" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -24530,18 +24530,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -24560,18 +24560,18 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="17" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
@@ -24598,7 +24598,7 @@
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
@@ -24817,7 +24817,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="54">
+    <row r="8" spans="1:26" ht="67.5">
       <c r="A8" s="3" t="s">
         <v>206</v>
       </c>
@@ -24845,10 +24845,10 @@
         <v>0.27536231884057971</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>242</v>
+        <v>207</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
@@ -24912,7 +24912,7 @@
         <v/>
       </c>
       <c r="G10" s="7" t="str">
-        <f t="shared" ref="G10:G12" si="2">IF(A10="","",C10)</f>
+        <f t="shared" ref="G5:G12" si="2">IF(A10="","",C10)</f>
         <v/>
       </c>
       <c r="H10" s="11" t="str">
@@ -30329,19 +30329,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
@@ -30359,19 +30359,19 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="17" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -30391,16 +30391,16 @@
     <row r="3" spans="1:26" ht="40.5">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -30507,7 +30507,7 @@
         <v>экономически оправдано</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>87</v>
@@ -30561,7 +30561,7 @@
         <v>экономически оправдано</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>88</v>
@@ -30615,7 +30615,7 @@
         <v>экономически оправдано</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>89</v>
@@ -30669,7 +30669,7 @@
         <v>экономически оправдано</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>90</v>
@@ -36166,18 +36166,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -36196,18 +36196,18 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="17" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
@@ -36334,7 +36334,7 @@
         <v>35824656</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -36386,7 +36386,7 @@
         <v>32242980</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -36438,7 +36438,7 @@
         <v>85306320</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
@@ -36490,7 +36490,7 @@
         <v>37617767.999999993</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
@@ -41995,20 +41995,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
@@ -42025,20 +42025,20 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="17" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -42410,7 +42410,7 @@
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="27">
+    <row r="13" spans="1:26">
       <c r="A13" s="3" t="str">
         <f>IF('02_Сегменты'!A5="","",'02_Сегменты'!A5)</f>
         <v>Финансовые аналитики и FP&amp;A</v>
@@ -42514,7 +42514,7 @@
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="27">
+    <row r="15" spans="1:26">
       <c r="A15" s="3" t="str">
         <f>IF('02_Сегменты'!A7="","",'02_Сегменты'!A7)</f>
         <v>Консультанты по управлению</v>
@@ -42566,7 +42566,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="27">
+    <row r="16" spans="1:26">
       <c r="A16" s="3" t="str">
         <f>IF('02_Сегменты'!A8="","",'02_Сегменты'!A8)</f>
         <v>МСП с финансовой функцией</v>
@@ -47913,20 +47913,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
@@ -47943,20 +47943,20 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="17" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -48008,7 +48008,7 @@
         <v>127</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>128</v>
@@ -48023,16 +48023,16 @@
         <v>131</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>132</v>
@@ -48054,7 +48054,7 @@
     </row>
     <row r="5" spans="1:26" ht="40.5">
       <c r="A5" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B5" s="7">
         <v>154111</v>
@@ -48090,7 +48090,7 @@
         <v>2449.0765320400001</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
@@ -48109,7 +48109,7 @@
     </row>
     <row r="6" spans="1:26" ht="40.5">
       <c r="A6" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B6" s="7">
         <v>35325</v>
@@ -48145,7 +48145,7 @@
         <v>2123.9765253</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
@@ -48164,7 +48164,7 @@
     </row>
     <row r="7" spans="1:26" ht="40.5">
       <c r="A7" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B7" s="7">
         <v>241737</v>
@@ -48200,7 +48200,7 @@
         <v>675.92662738799993</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
@@ -48219,7 +48219,7 @@
     </row>
     <row r="8" spans="1:26" ht="40.5">
       <c r="A8" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B8" s="7">
         <v>202178</v>
@@ -48255,7 +48255,7 @@
         <v>1683.7432362720001</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
@@ -48274,7 +48274,7 @@
     </row>
     <row r="9" spans="1:26" ht="40.5">
       <c r="A9" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B9" s="7">
         <v>14688</v>
@@ -48310,7 +48310,7 @@
         <v>1134.2855589119999</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
@@ -48329,7 +48329,7 @@
     </row>
     <row r="10" spans="1:26" ht="40.5">
       <c r="A10" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B10" s="7">
         <v>17824</v>
@@ -48365,7 +48365,7 @@
         <v>1347.0632730879997</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
@@ -48384,7 +48384,7 @@
     </row>
     <row r="11" spans="1:26" ht="40.5">
       <c r="A11" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B11" s="7">
         <v>292214</v>
@@ -48420,7 +48420,7 @@
         <v>1363.737023168</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
@@ -48439,7 +48439,7 @@
     </row>
     <row r="12" spans="1:26" ht="40.5">
       <c r="A12" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B12" s="7">
         <v>116617</v>
@@ -48475,7 +48475,7 @@
         <v>907.85075036400019</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
@@ -48494,7 +48494,7 @@
     </row>
     <row r="13" spans="1:26" ht="40.5">
       <c r="A13" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B13" s="7">
         <v>222359</v>
@@ -48530,7 +48530,7 @@
         <v>4611.6358269639995</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
@@ -48549,7 +48549,7 @@
     </row>
     <row r="14" spans="1:26" ht="40.5">
       <c r="A14" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B14" s="7">
         <v>701540</v>
@@ -48585,7 +48585,7 @@
         <v>987.85250480000002</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -48604,7 +48604,7 @@
     </row>
     <row r="15" spans="1:26" ht="40.5">
       <c r="A15" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B15" s="7">
         <v>1935</v>
@@ -48640,7 +48640,7 @@
         <v>167.14163123999998</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
@@ -48659,7 +48659,7 @@
     </row>
     <row r="16" spans="1:26" ht="40.5">
       <c r="A16" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B16" s="7">
         <v>5522</v>
@@ -48695,7 +48695,7 @@
         <v>94.973871959999997</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
@@ -54032,18 +54032,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -54062,18 +54062,18 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="17" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
@@ -54528,11 +54528,11 @@
       <c r="Z14" s="2"/>
     </row>
     <row r="15" spans="1:26" ht="13.9">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -54558,12 +54558,12 @@
       <c r="Z15" s="2"/>
     </row>
     <row r="16" spans="1:26">
-      <c r="A16" s="20" t="str">
+      <c r="A16" s="19" t="str">
         <f>IF(B7&gt;=1,"Платежеспособность сегментов в среднем достаточная: бюджет клиентов сопоставим с ценой предложения. Рекомендуется переходить к проверке конкурентов, каналов продаж и пилотному запуску.","Платежеспособность сегментов требует дополнительной проверки: цена предложения выше доступного бюджета. Нужно уточнить сегменты, снизить стоимость входного продукта или изменить состав предложения.")</f>
         <v>Платежеспособность сегментов в среднем достаточная: бюджет клиентов сопоставим с ценой предложения. Рекомендуется переходить к проверке конкурентов, каналов продаж и пилотному запуску.</v>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
@@ -54589,9 +54589,9 @@
       <c r="Z16" s="2"/>
     </row>
     <row r="17" spans="1:26">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
+      <c r="A17" s="16"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
@@ -54617,9 +54617,9 @@
       <c r="Z17" s="2"/>
     </row>
     <row r="18" spans="1:26">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
+      <c r="A18" s="16"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>

--- a/ЛР2-3_Объем_рынка/Excel/ЛР2-3_3_платежеспособность_TableMind.xlsx
+++ b/ЛР2-3_Объем_рынка/Excel/ЛР2-3_3_платежеспособность_TableMind.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-project-continuation-447426\ЛР2-3_Объем_рынка\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{792BCD86-16A7-429B-812F-5D75B42766E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED895228-25EA-4FBB-A8C0-637278FB34B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2205" yWindow="458" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -768,10 +768,10 @@
     <t>ЛР1, Материалы_собранные</t>
   </si>
   <si>
-    <t>Опросы / интервью (модельные данные)</t>
+    <t>Расчет ценовой чувствительности по профилям клиентов</t>
   </si>
   <si>
-    <t>Модельные данные по решению автора (Р-8); реального опроса не проводилось</t>
+    <t>Расчет по параметрам сегментов (допущение Д-30), приложение Г отчета</t>
   </si>
 </sst>
 </file>
@@ -1000,7 +1000,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4F5D-4A80-8680-58C1E99B1BE4}"/>
+              <c16:uniqueId val="{00000000-1C5B-4F79-A406-F2A1026147A6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1048,7 +1048,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-4F5D-4A80-8680-58C1E99B1BE4}"/>
+              <c16:uniqueId val="{00000001-1C5B-4F79-A406-F2A1026147A6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1209,7 +1209,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-AB72-4393-98E5-15D3D4942C6C}"/>
+              <c16:uniqueId val="{00000000-297F-4B1B-B922-75A800B714CE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7641,7 +7641,7 @@
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
     </row>
-    <row r="10" spans="1:26" ht="27">
+    <row r="10" spans="1:26" ht="40.5">
       <c r="A10" s="3" t="s">
         <v>241</v>
       </c>
